--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -512,7 +512,7 @@
         <v>22866.5</v>
       </c>
       <c r="J2" t="n">
-        <v>16.53000068664551</v>
+        <v>16.51000022888184</v>
       </c>
       <c r="K2" t="n">
         <v>22866.5</v>
@@ -15458,7 +15458,7 @@
         <v>0.2</v>
       </c>
       <c r="J2" t="n">
-        <v>4.03</v>
+        <v>3.9</v>
       </c>
       <c r="K2" t="n">
         <v>0.2</v>
@@ -30404,7 +30404,7 @@
         <v>-0.37</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="K2" t="n">
         <v>-0.37</v>
@@ -45298,7 +45298,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.03</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="7">
@@ -52797,7 +52797,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3.35%</t>
+          <t>3.34%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -504,7 +504,7 @@
         <v>22840.55078125</v>
       </c>
       <c r="I2" t="n">
-        <v>16.47999954223633</v>
+        <v>16.32999992370605</v>
       </c>
       <c r="J2" t="n">
         <v>22840.55078125</v>
@@ -536,7 +536,7 @@
         <v>22654.650390625</v>
       </c>
       <c r="I3" t="n">
-        <v>16.22999954223633</v>
+        <v>16.32999992370605</v>
       </c>
       <c r="J3" t="n">
         <v>22654.650390625</v>
@@ -14330,7 +14330,7 @@
         <v>0.09</v>
       </c>
       <c r="I2" t="n">
-        <v>3.71</v>
+        <v>2.77</v>
       </c>
       <c r="J2" t="n">
         <v>0.09</v>
@@ -14362,7 +14362,7 @@
         <v>-0.72</v>
       </c>
       <c r="I3" t="n">
-        <v>2.14</v>
+        <v>2.77</v>
       </c>
       <c r="J3" t="n">
         <v>-0.72</v>
@@ -28156,7 +28156,7 @@
         <v>0.82</v>
       </c>
       <c r="I2" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0.82</v>
@@ -28188,7 +28188,7 @@
         <v>0.54</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="J3" t="n">
         <v>0.54</v>
@@ -41930,7 +41930,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.71</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="6">
@@ -42022,12 +42022,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nifty500 Multicap 50:25:25, Nifty Midcap 150, Nifty Next 50</t>
+          <t>Nifty Midcap 150, Nifty Next 50, Nifty Midcap 50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nifty 50, Nifty 100, Nifty 200</t>
+          <t>Nifty500 Multicap 50:25:25, Nifty 50, Nifty 100</t>
         </is>
       </c>
     </row>
@@ -42044,7 +42044,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nifty500 Multicap 50:25:25, Nifty 50, Nifty 100</t>
+          <t>Nifty 50, Nifty 100, Nifty 200</t>
         </is>
       </c>
     </row>
@@ -49501,7 +49501,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>2.65%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -504,7 +504,7 @@
         <v>22840.55078125</v>
       </c>
       <c r="I2" t="n">
-        <v>16.32999992370605</v>
+        <v>16.47999954223633</v>
       </c>
       <c r="J2" t="n">
         <v>22840.55078125</v>
@@ -14330,7 +14330,7 @@
         <v>0.09</v>
       </c>
       <c r="I2" t="n">
-        <v>2.77</v>
+        <v>3.71</v>
       </c>
       <c r="J2" t="n">
         <v>0.09</v>
@@ -28156,7 +28156,7 @@
         <v>0.82</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="J2" t="n">
         <v>0.82</v>
@@ -41930,7 +41930,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.77</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="6">
@@ -42022,12 +42022,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150, Nifty Next 50, Nifty Midcap 50</t>
+          <t>Nifty Midcap 150, Nifty Next 50, Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nifty500 Multicap 50:25:25, Nifty 50, Nifty 100</t>
+          <t>Nifty 50, Nifty 100, Nifty 200</t>
         </is>
       </c>
     </row>
@@ -49501,7 +49501,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.65%</t>
+          <t>2.76%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -480,34 +480,34 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B2" t="n">
-        <v>23329</v>
+        <v>23446.80078125</v>
       </c>
       <c r="C2" t="n">
-        <v>71804.046875</v>
+        <v>72462.3984375</v>
       </c>
       <c r="D2" t="n">
-        <v>24469.75</v>
+        <v>24612.25</v>
       </c>
       <c r="E2" t="n">
-        <v>13613.400390625</v>
+        <v>13695.9501953125</v>
       </c>
       <c r="F2" t="n">
-        <v>17878.599609375</v>
+        <v>17979.650390625</v>
       </c>
       <c r="G2" t="n">
-        <v>22787.19921875</v>
+        <v>22928.849609375</v>
       </c>
       <c r="H2" t="n">
-        <v>22794.19921875</v>
+        <v>22935.099609375</v>
       </c>
       <c r="I2" t="n">
-        <v>16.45000076293945</v>
+        <v>16.53000068664551</v>
       </c>
       <c r="J2" t="n">
-        <v>22794.19921875</v>
+        <v>22935.099609375</v>
       </c>
     </row>
     <row r="3">
@@ -536,7 +536,7 @@
         <v>22860.05078125</v>
       </c>
       <c r="I3" t="n">
-        <v>16.47999954223633</v>
+        <v>16.48999977111816</v>
       </c>
       <c r="J3" t="n">
         <v>22860.05078125</v>
@@ -14370,34 +14370,34 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.74</v>
+        <v>-1.25</v>
       </c>
       <c r="C2" t="n">
-        <v>5.21</v>
+        <v>6.18</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.23</v>
+        <v>-1.66</v>
       </c>
       <c r="E2" t="n">
-        <v>1.12</v>
+        <v>1.73</v>
       </c>
       <c r="F2" t="n">
-        <v>10.08</v>
+        <v>10.7</v>
       </c>
       <c r="G2" t="n">
-        <v>7.25</v>
+        <v>7.92</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.11</v>
+        <v>0.51</v>
       </c>
       <c r="I2" t="n">
-        <v>3.52</v>
+        <v>4.03</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.11</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="3">
@@ -14426,7 +14426,7 @@
         <v>0.18</v>
       </c>
       <c r="I3" t="n">
-        <v>3.71</v>
+        <v>3.78</v>
       </c>
       <c r="J3" t="n">
         <v>0.18</v>
@@ -28260,34 +28260,34 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.36</v>
+        <v>0.14</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.39</v>
+        <v>0.53</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.37</v>
+        <v>0.21</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.31</v>
+        <v>0.29</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.01</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.13</v>
+        <v>0.49</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.29</v>
+        <v>0.33</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.18</v>
+        <v>0.24</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.29</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="3">
@@ -28316,7 +28316,7 @@
         <v>0.09</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="J3" t="n">
         <v>0.09</v>
@@ -42092,7 +42092,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.08</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="3">
@@ -42102,7 +42102,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.25</v>
+        <v>7.92</v>
       </c>
     </row>
     <row r="4">
@@ -42112,7 +42112,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.21</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="5">
@@ -42122,7 +42122,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.52</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="6">
@@ -42132,7 +42132,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.12</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="7">
@@ -42142,7 +42142,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.11</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="8">
@@ -42152,7 +42152,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.11</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="9">
@@ -42162,7 +42162,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-1.74</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="10">
@@ -42172,7 +42172,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-2.23</v>
+        <v>-1.66</v>
       </c>
     </row>
   </sheetData>
@@ -42209,17 +42209,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>22-Sep-26</t>
+          <t>23-Sep-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nifty Midcap 50, Nifty Midcap 150, Nifty500 Multicap 50:25:25</t>
+          <t>Nifty Midcap 50, Nifty Next 50, Nifty Midcap 150</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty 100, Nifty 50</t>
+          <t>Nifty 50, Nifty 100, Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
     </row>
@@ -49727,7 +49727,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>3.19%</t>
         </is>
       </c>
     </row>
@@ -49739,7 +49739,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -49751,7 +49751,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -483,31 +483,31 @@
         <v>46290</v>
       </c>
       <c r="B2" t="n">
-        <v>23063.099609375</v>
+        <v>23140.5</v>
       </c>
       <c r="C2" t="n">
-        <v>71381.453125</v>
+        <v>71778.6484375</v>
       </c>
       <c r="D2" t="n">
-        <v>24216.19921875</v>
+        <v>24307.55078125</v>
       </c>
       <c r="E2" t="n">
-        <v>13457.5498046875</v>
+        <v>13494.2001953125</v>
       </c>
       <c r="F2" t="n">
-        <v>17518.05078125</v>
+        <v>17474.099609375</v>
       </c>
       <c r="G2" t="n">
-        <v>22469.900390625</v>
+        <v>22437</v>
       </c>
       <c r="H2" t="n">
-        <v>22552.599609375</v>
+        <v>22603.5</v>
       </c>
       <c r="I2" t="n">
-        <v>16.53000068664551</v>
+        <v>16.30999946594238</v>
       </c>
       <c r="J2" t="n">
-        <v>22552.599609375</v>
+        <v>22603.5</v>
       </c>
     </row>
     <row r="3">
@@ -536,7 +536,7 @@
         <v>22552.599609375</v>
       </c>
       <c r="I3" t="n">
-        <v>16.53000068664551</v>
+        <v>16.30999946594238</v>
       </c>
       <c r="J3" t="n">
         <v>22552.599609375</v>
@@ -14469,31 +14469,31 @@
         <v>46290</v>
       </c>
       <c r="B2" t="n">
-        <v>-2.86</v>
+        <v>-2.54</v>
       </c>
       <c r="C2" t="n">
-        <v>4.59</v>
+        <v>5.17</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.25</v>
+        <v>-2.88</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.04</v>
+        <v>0.24</v>
       </c>
       <c r="F2" t="n">
-        <v>7.86</v>
+        <v>7.59</v>
       </c>
       <c r="G2" t="n">
-        <v>5.76</v>
+        <v>5.6</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.17</v>
+        <v>-0.95</v>
       </c>
       <c r="I2" t="n">
-        <v>4.03</v>
+        <v>2.64</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.17</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="3">
@@ -14522,7 +14522,7 @@
         <v>-1.17</v>
       </c>
       <c r="I3" t="n">
-        <v>4.03</v>
+        <v>2.64</v>
       </c>
       <c r="J3" t="n">
         <v>-1.17</v>
@@ -28455,31 +28455,31 @@
         <v>46290</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="3">
@@ -28508,7 +28508,7 @@
         <v>-1.67</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-1.33</v>
       </c>
       <c r="J3" t="n">
         <v>-1.67</v>
@@ -42380,7 +42380,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.86</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="3">
@@ -42390,7 +42390,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.76</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="4">
@@ -42400,7 +42400,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.59</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="5">
@@ -42410,7 +42410,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.03</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="6">
@@ -42420,7 +42420,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.04</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="7">
@@ -42430,7 +42430,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-1.17</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="8">
@@ -42440,7 +42440,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1.17</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="9">
@@ -42450,7 +42450,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-2.86</v>
+        <v>-2.54</v>
       </c>
     </row>
     <row r="10">
@@ -42460,7 +42460,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-3.25</v>
+        <v>-2.88</v>
       </c>
     </row>
   </sheetData>
@@ -42502,12 +42502,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nifty 50, Nifty Next 50, Nifty 100</t>
+          <t>Nifty Next 50, Nifty 100, Nifty 50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nifty 50, Nifty Next 50, Nifty 100</t>
+          <t>Nifty Midcap 50, Nifty Midcap 150, Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
     </row>
@@ -50066,7 +50066,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.55%</t>
         </is>
       </c>
     </row>
@@ -50078,7 +50078,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -50090,7 +50090,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -504,7 +504,7 @@
         <v>22603.5</v>
       </c>
       <c r="I2" t="n">
-        <v>16.30999946594238</v>
+        <v>16.29000091552734</v>
       </c>
       <c r="J2" t="n">
         <v>22603.5</v>
@@ -14490,7 +14490,7 @@
         <v>-0.95</v>
       </c>
       <c r="I2" t="n">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
       <c r="J2" t="n">
         <v>-0.95</v>
@@ -28476,7 +28476,7 @@
         <v>0.23</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="J2" t="n">
         <v>0.23</v>
@@ -42410,7 +42410,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="6">
@@ -50066,7 +50066,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.53%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -483,31 +483,31 @@
         <v>46296</v>
       </c>
       <c r="B2" t="n">
-        <v>22620.44921875</v>
+        <v>22421.94921875</v>
       </c>
       <c r="C2" t="n">
-        <v>69746.953125</v>
+        <v>68981.3515625</v>
       </c>
       <c r="D2" t="n">
-        <v>23734.69921875</v>
+        <v>23516.5</v>
       </c>
       <c r="E2" t="n">
-        <v>13169.9501953125</v>
+        <v>13046.4501953125</v>
       </c>
       <c r="F2" t="n">
-        <v>17028.69921875</v>
+        <v>16840.349609375</v>
       </c>
       <c r="G2" t="n">
-        <v>21867.5</v>
+        <v>21643.849609375</v>
       </c>
       <c r="H2" t="n">
-        <v>22072.099609375</v>
+        <v>21857.75</v>
       </c>
       <c r="I2" t="n">
-        <v>15.96000003814697</v>
+        <v>15.94999980926514</v>
       </c>
       <c r="J2" t="n">
-        <v>22072.099609375</v>
+        <v>21857.75</v>
       </c>
     </row>
     <row r="3">
@@ -536,7 +536,7 @@
         <v>22072.099609375</v>
       </c>
       <c r="I3" t="n">
-        <v>15.96000003814697</v>
+        <v>15.94999980926514</v>
       </c>
       <c r="J3" t="n">
         <v>22072.099609375</v>
@@ -14597,31 +14597,31 @@
         <v>46296</v>
       </c>
       <c r="B2" t="n">
-        <v>-4.73</v>
+        <v>-5.56</v>
       </c>
       <c r="C2" t="n">
-        <v>2.2</v>
+        <v>1.07</v>
       </c>
       <c r="D2" t="n">
-        <v>-5.17</v>
+        <v>-6.04</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.17</v>
+        <v>-3.09</v>
       </c>
       <c r="F2" t="n">
-        <v>4.84</v>
+        <v>3.68</v>
       </c>
       <c r="G2" t="n">
-        <v>2.92</v>
+        <v>1.87</v>
       </c>
       <c r="H2" t="n">
-        <v>-3.28</v>
+        <v>-4.22</v>
       </c>
       <c r="I2" t="n">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="J2" t="n">
-        <v>-3.28</v>
+        <v>-4.22</v>
       </c>
     </row>
     <row r="3">
@@ -14650,7 +14650,7 @@
         <v>-3.28</v>
       </c>
       <c r="I3" t="n">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="J3" t="n">
         <v>-3.28</v>
@@ -28711,31 +28711,31 @@
         <v>46296</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>-0.88</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>-1.1</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-0.92</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-1.11</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-1.02</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0.97</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="3">
@@ -28764,7 +28764,7 @@
         <v>-0.13</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="J3" t="n">
         <v>-0.13</v>
@@ -42764,7 +42764,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.84</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="3">
@@ -42774,7 +42774,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.92</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="4">
@@ -42784,7 +42784,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.2</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="5">
@@ -42794,7 +42794,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="6">
@@ -42804,7 +42804,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-2.17</v>
+        <v>-3.09</v>
       </c>
     </row>
     <row r="7">
@@ -42814,7 +42814,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-3.28</v>
+        <v>-4.22</v>
       </c>
     </row>
     <row r="8">
@@ -42824,7 +42824,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-3.28</v>
+        <v>-4.22</v>
       </c>
     </row>
     <row r="9">
@@ -42834,7 +42834,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-4.73</v>
+        <v>-5.56</v>
       </c>
     </row>
     <row r="10">
@@ -42844,7 +42844,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-5.17</v>
+        <v>-6.04</v>
       </c>
     </row>
   </sheetData>
@@ -42886,12 +42886,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nifty 50, Nifty Next 50, Nifty 100</t>
+          <t>Nifty500 Multicap 50:25:25, Nifty 50, Nifty 100</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nifty 50, Nifty Next 50, Nifty 100</t>
+          <t>Nifty Midcap 50, Nifty Next 50, Nifty Midcap 150</t>
         </is>
       </c>
     </row>
@@ -42903,7 +42903,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 150, Nifty500 Multicap 50:25:25</t>
+          <t>Nifty Next 50, Nifty Midcap 150, Nifty Midcap 50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -50518,7 +50518,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>-1.79%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -483,31 +483,31 @@
         <v>46304</v>
       </c>
       <c r="B2" t="n">
-        <v>22231.80078125</v>
+        <v>22520.44921875</v>
       </c>
       <c r="C2" t="n">
-        <v>67614.5</v>
+        <v>68166.703125</v>
       </c>
       <c r="D2" t="n">
-        <v>23266.75</v>
+        <v>23547.900390625</v>
       </c>
       <c r="E2" t="n">
-        <v>12897.7998046875</v>
+        <v>13062.849609375</v>
       </c>
       <c r="F2" t="n">
-        <v>16530.900390625</v>
+        <v>16786.69921875</v>
       </c>
       <c r="G2" t="n">
-        <v>21311.5</v>
+        <v>21603.25</v>
       </c>
       <c r="H2" t="n">
-        <v>21616.150390625</v>
+        <v>21866.650390625</v>
       </c>
       <c r="I2" t="n">
-        <v>15.94999980926514</v>
+        <v>15.60999965667725</v>
       </c>
       <c r="J2" t="n">
-        <v>21616.150390625</v>
+        <v>21866.650390625</v>
       </c>
     </row>
     <row r="3">
@@ -536,7 +536,7 @@
         <v>21616.150390625</v>
       </c>
       <c r="I3" t="n">
-        <v>15.94999980926514</v>
+        <v>15.60999965667725</v>
       </c>
       <c r="J3" t="n">
         <v>21616.150390625</v>
@@ -14629,31 +14629,31 @@
         <v>46304</v>
       </c>
       <c r="B2" t="n">
-        <v>-6.36</v>
+        <v>-5.15</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.93</v>
+        <v>-0.12</v>
       </c>
       <c r="D2" t="n">
-        <v>-7.04</v>
+        <v>-5.92</v>
       </c>
       <c r="E2" t="n">
-        <v>-4.19</v>
+        <v>-2.97</v>
       </c>
       <c r="F2" t="n">
-        <v>1.78</v>
+        <v>3.35</v>
       </c>
       <c r="G2" t="n">
-        <v>0.31</v>
+        <v>1.68</v>
       </c>
       <c r="H2" t="n">
-        <v>-5.27</v>
+        <v>-4.18</v>
       </c>
       <c r="I2" t="n">
-        <v>0.38</v>
+        <v>-1.76</v>
       </c>
       <c r="J2" t="n">
-        <v>-5.27</v>
+        <v>-4.18</v>
       </c>
     </row>
     <row r="3">
@@ -14682,7 +14682,7 @@
         <v>-5.27</v>
       </c>
       <c r="I3" t="n">
-        <v>0.38</v>
+        <v>-1.76</v>
       </c>
       <c r="J3" t="n">
         <v>-5.27</v>
@@ -28775,31 +28775,31 @@
         <v>46304</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="3">
@@ -28828,7 +28828,7 @@
         <v>-2.01</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-2.13</v>
       </c>
       <c r="J3" t="n">
         <v>-2.01</v>
@@ -42860,37 +42860,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.78</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nifty500 Multicap 50:25:25</t>
+          <t>Nifty Midcap 150</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.38</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150</t>
+          <t>Nifty Next 50</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.31</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Nifty Next 50</t>
+          <t>Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.93</v>
+        <v>-1.76</v>
       </c>
     </row>
     <row r="6">
@@ -42900,7 +42900,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-4.19</v>
+        <v>-2.97</v>
       </c>
     </row>
     <row r="7">
@@ -42910,7 +42910,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-5.27</v>
+        <v>-4.18</v>
       </c>
     </row>
     <row r="8">
@@ -42920,7 +42920,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-5.27</v>
+        <v>-4.18</v>
       </c>
     </row>
     <row r="9">
@@ -42930,7 +42930,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-6.36</v>
+        <v>-5.15</v>
       </c>
     </row>
     <row r="10">
@@ -42940,7 +42940,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-7.04</v>
+        <v>-5.92</v>
       </c>
     </row>
   </sheetData>
@@ -42982,12 +42982,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nifty 50, Nifty Next 50, Nifty 100</t>
+          <t>Nifty Midcap 50, Nifty Midcap 150, Nifty 50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nifty 50, Nifty Next 50, Nifty 100</t>
+          <t>Nifty500 Multicap 50:25:25, Nifty Next 50, Nifty500 LargeMidSmall Equal-Cap Weighted</t>
         </is>
       </c>
     </row>
@@ -42999,7 +42999,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nifty500 Multicap 50:25:25, Nifty 50, Nifty 100</t>
+          <t>Nifty 50, Nifty 100, Nifty 200</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -50631,7 +50631,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-2.14%</t>
         </is>
       </c>
     </row>
@@ -50643,7 +50643,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -50655,7 +50655,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -504,7 +504,7 @@
         <v>21866.650390625</v>
       </c>
       <c r="I2" t="n">
-        <v>15.60999965667725</v>
+        <v>15.77000045776367</v>
       </c>
       <c r="J2" t="n">
         <v>21866.650390625</v>
@@ -14650,7 +14650,7 @@
         <v>-4.18</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.76</v>
+        <v>-0.76</v>
       </c>
       <c r="J2" t="n">
         <v>-4.18</v>
@@ -28796,7 +28796,7 @@
         <v>1.16</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="J2" t="n">
         <v>1.16</v>
@@ -42890,7 +42890,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.76</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="6">
@@ -42987,7 +42987,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nifty500 Multicap 50:25:25, Nifty Next 50, Nifty500 LargeMidSmall Equal-Cap Weighted</t>
+          <t>Nifty Next 50, Nifty500 Multicap 50:25:25, Nifty500 LargeMidSmall Equal-Cap Weighted</t>
         </is>
       </c>
     </row>
@@ -50631,7 +50631,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-2.14%</t>
+          <t>-2.03%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -504,7 +504,7 @@
         <v>22270.05078125</v>
       </c>
       <c r="I2" t="n">
-        <v>16</v>
+        <v>15.9399995803833</v>
       </c>
       <c r="J2" t="n">
         <v>22270.05078125</v>
@@ -536,7 +536,7 @@
         <v>22180.80078125</v>
       </c>
       <c r="I3" t="n">
-        <v>15.89999961853027</v>
+        <v>15.9399995803833</v>
       </c>
       <c r="J3" t="n">
         <v>22180.80078125</v>
@@ -14810,7 +14810,7 @@
         <v>-2.41</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.31</v>
       </c>
       <c r="J2" t="n">
         <v>-2.41</v>
@@ -14842,7 +14842,7 @@
         <v>-2.8</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06</v>
+        <v>0.31</v>
       </c>
       <c r="J3" t="n">
         <v>-2.8</v>
@@ -29116,7 +29116,7 @@
         <v>0.4</v>
       </c>
       <c r="I2" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0.4</v>
@@ -29148,7 +29148,7 @@
         <v>0.65</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="J3" t="n">
         <v>0.65</v>
@@ -43370,7 +43370,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="6">
@@ -43462,12 +43462,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nifty 50, Nifty500 Multicap 50:25:25, Nifty 100</t>
+          <t>Nifty 50, Nifty 100, Nifty 200</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150, Nifty Midcap 50, Nifty500 LargeMidSmall Equal-Cap Weighted</t>
+          <t>Nifty Midcap 150, Nifty Midcap 50, Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
     </row>
@@ -51196,7 +51196,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>-0.42%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -504,7 +504,7 @@
         <v>22270.05078125</v>
       </c>
       <c r="I2" t="n">
-        <v>15.9399995803833</v>
+        <v>16</v>
       </c>
       <c r="J2" t="n">
         <v>22270.05078125</v>
@@ -14810,7 +14810,7 @@
         <v>-2.41</v>
       </c>
       <c r="I2" t="n">
-        <v>0.31</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J2" t="n">
         <v>-2.41</v>
@@ -29116,7 +29116,7 @@
         <v>0.4</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="J2" t="n">
         <v>0.4</v>
@@ -43370,7 +43370,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.31</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -51196,7 +51196,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -483,31 +483,31 @@
         <v>46314</v>
       </c>
       <c r="B2" t="n">
-        <v>23146.150390625</v>
+        <v>22888.94921875</v>
       </c>
       <c r="C2" t="n">
-        <v>68988.6015625</v>
+        <v>68695.8515625</v>
       </c>
       <c r="D2" t="n">
-        <v>24133.099609375</v>
+        <v>23895.44921875</v>
       </c>
       <c r="E2" t="n">
-        <v>13337.400390625</v>
+        <v>13203.349609375</v>
       </c>
       <c r="F2" t="n">
-        <v>16946.30078125</v>
+        <v>16767.849609375</v>
       </c>
       <c r="G2" t="n">
-        <v>21736.75</v>
+        <v>21499.30078125</v>
       </c>
       <c r="H2" t="n">
-        <v>22270.05078125</v>
+        <v>22041.599609375</v>
       </c>
       <c r="I2" t="n">
-        <v>16</v>
+        <v>15.84000015258789</v>
       </c>
       <c r="J2" t="n">
-        <v>22270.05078125</v>
+        <v>22041.599609375</v>
       </c>
     </row>
     <row r="3">
@@ -14821,31 +14821,31 @@
         <v>46314</v>
       </c>
       <c r="B2" t="n">
-        <v>-2.51</v>
+        <v>-3.6</v>
       </c>
       <c r="C2" t="n">
-        <v>1.09</v>
+        <v>0.66</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.58</v>
+        <v>-4.53</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.93</v>
+        <v>-1.92</v>
       </c>
       <c r="F2" t="n">
-        <v>4.34</v>
+        <v>3.24</v>
       </c>
       <c r="G2" t="n">
-        <v>2.31</v>
+        <v>1.19</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.41</v>
+        <v>-3.41</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.31</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.41</v>
+        <v>-3.41</v>
       </c>
     </row>
     <row r="3">
@@ -29159,31 +29159,31 @@
         <v>46314</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>-1.11</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>-0.42</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-0.98</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>-1.01</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-1.05</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-1.09</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-1.03</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="3">
@@ -43436,7 +43436,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.34</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="3">
@@ -43446,7 +43446,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.31</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="4">
@@ -43456,7 +43456,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.09</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="5">
@@ -43466,7 +43466,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="6">
@@ -43476,7 +43476,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.93</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="7">
@@ -43486,7 +43486,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-2.41</v>
+        <v>-3.41</v>
       </c>
     </row>
     <row r="8">
@@ -43496,7 +43496,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-2.41</v>
+        <v>-3.41</v>
       </c>
     </row>
     <row r="9">
@@ -43506,7 +43506,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-2.51</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="10">
@@ -43516,7 +43516,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-3.58</v>
+        <v>-4.53</v>
       </c>
     </row>
   </sheetData>
@@ -43558,12 +43558,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nifty 50, Nifty Next 50, Nifty 100</t>
+          <t>Nifty Next 50, Nifty 100, Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nifty 50, Nifty Next 50, Nifty 100</t>
+          <t>Nifty 50, Nifty Midcap 150, Nifty Midcap 50</t>
         </is>
       </c>
     </row>
@@ -51309,7 +51309,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>-1.34%</t>
         </is>
       </c>
     </row>
@@ -51321,7 +51321,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -51333,7 +51333,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_raw.xlsx
+++ b/nse_indices_1_raw.xlsx
@@ -483,31 +483,31 @@
         <v>46318</v>
       </c>
       <c r="B2" t="n">
-        <v>22687.650390625</v>
+        <v>22600</v>
       </c>
       <c r="C2" t="n">
-        <v>67354.1484375</v>
+        <v>65828.6015625</v>
       </c>
       <c r="D2" t="n">
-        <v>23637.80078125</v>
+        <v>23465.05078125</v>
       </c>
       <c r="E2" t="n">
-        <v>13025.5</v>
+        <v>12892.400390625</v>
       </c>
       <c r="F2" t="n">
-        <v>16410.80078125</v>
+        <v>16066.400390625</v>
       </c>
       <c r="G2" t="n">
-        <v>21028.650390625</v>
+        <v>20592.75</v>
       </c>
       <c r="H2" t="n">
-        <v>21696.55078125</v>
+        <v>21427.599609375</v>
       </c>
       <c r="I2" t="n">
-        <v>15.47999954223633</v>
+        <v>15.25</v>
       </c>
       <c r="J2" t="n">
-        <v>21696.55078125</v>
+        <v>21427.599609375</v>
       </c>
     </row>
     <row r="3">
@@ -14917,31 +14917,31 @@
         <v>46318</v>
       </c>
       <c r="B2" t="n">
-        <v>-4.44</v>
+        <v>-4.81</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.31</v>
+        <v>-3.54</v>
       </c>
       <c r="D2" t="n">
-        <v>-5.56</v>
+        <v>-6.25</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.25</v>
+        <v>-4.23</v>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>-1.08</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.03</v>
+        <v>-3.08</v>
       </c>
       <c r="H2" t="n">
-        <v>-4.92</v>
+        <v>-6.1</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.58</v>
+        <v>-4.03</v>
       </c>
       <c r="J2" t="n">
-        <v>-4.92</v>
+        <v>-6.1</v>
       </c>
     </row>
     <row r="3">
@@ -29351,31 +29351,31 @@
         <v>46318</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>-0.39</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>-2.26</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-0.73</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>-1.02</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-2.1</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-2.07</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-1.24</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-1.49</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="3">
@@ -43724,7 +43724,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.04</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="3">
@@ -43734,7 +43734,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-1.03</v>
+        <v>-3.08</v>
       </c>
     </row>
     <row r="4">
@@ -43744,7 +43744,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-1.31</v>
+        <v>-3.54</v>
       </c>
     </row>
     <row r="5">
@@ -43754,7 +43754,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-2.58</v>
+        <v>-4.03</v>
       </c>
     </row>
     <row r="6">
@@ -43764,7 +43764,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-3.25</v>
+        <v>-4.23</v>
       </c>
     </row>
     <row r="7">
@@ -43774,7 +43774,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-4.44</v>
+        <v>-4.81</v>
       </c>
     </row>
     <row r="8">
@@ -43784,7 +43784,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-4.92</v>
+        <v>-6.1</v>
       </c>
     </row>
     <row r="9">
@@ -43794,7 +43794,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-4.92</v>
+        <v>-6.1</v>
       </c>
     </row>
     <row r="10">
@@ -43804,7 +43804,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-5.56</v>
+        <v>-6.25</v>
       </c>
     </row>
   </sheetData>
@@ -43846,12 +43846,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nifty 50, Nifty Next 50, Nifty 100</t>
+          <t>Nifty 50, Nifty 100, Nifty 200</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nifty 50, Nifty Next 50, Nifty 100</t>
+          <t>Nifty Next 50, Nifty Midcap 50, Nifty Midcap 150</t>
         </is>
       </c>
     </row>
@@ -51560,7 +51560,7 @@
         <v>11</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -51648,7 +51648,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-4.36%</t>
         </is>
       </c>
     </row>
@@ -51660,7 +51660,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -51672,7 +51672,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
     </row>
